--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-23.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-23.xlsx
@@ -474,712 +474,712 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583991746006</v>
+        <v>5583987558685</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liriane</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liriane Machado Bezerra</t>
+          <t>Cristiane Felix da Silva Santos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583982108404</v>
+        <v>5583996998233</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jaqueline</t>
+          <t>Tania</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jaqueline Bispo dos Santos</t>
+          <t>Tania do Carmo Pessoa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583987602629</v>
+        <v>5583986610779</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mayara</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mayara Teixeira de Sousa</t>
+          <t>Jean Kleber Santos da Silva</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583988656618</v>
+        <v>5511910916798</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Innovasan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Felipe Rodrigues dos Santos</t>
+          <t>Innovasan</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583999428747</v>
+        <v>5592991914004</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carolina Maia</t>
+          <t>Manoel Espinola</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583988507143</v>
+        <v>5583986855845</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Jonatha</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Elaine Pereira de Souza</t>
+          <t>Jonatha Ferreira da Silva</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583987147769</v>
+        <v>5583988409906</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reginaldo</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reginaldo Frutuoso de Sousa</t>
+          <t>Charles Eduardo Soares de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583986239122</v>
+        <v>5583999685044</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Edgar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Franklin Figueiredo de Almeida</t>
+          <t>Edgar Luis Almeida da Silva</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583988638711</v>
+        <v>5583987295739</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Solange</t>
+          <t>Tiago</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Solange Rodrigues</t>
+          <t>Tiago Justino</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583988146936</v>
+        <v>5583988388764</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zuleide</t>
+          <t>Aluisio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zuleide da Silva</t>
+          <t>Aluisio Ferreira de Santana Filho</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583998373500</v>
+        <v>5583991741951</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jonathas</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonathas Paulo dos Santos Catao</t>
+          <t>Residencial Florenca Ii</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5593999014750</v>
+        <v>5583996158493</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lucelio</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lucelio de Araujo Morais</t>
+          <t>Adriana Almeida Martins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583986690357</v>
+        <v>5583987264017</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jocimo</t>
+          <t>Ug-</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jocimo Freire dos Santos</t>
+          <t>Ug- Construtora</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583987084613</v>
+        <v>5583986951266</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gledson</t>
+          <t>Severino</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gledson Soares da Soledade</t>
+          <t>Severino Gomes Bezerra</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583993940979</v>
+        <v>5583986592015</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Antonio Fernandes Lemos</t>
+          <t>Jose Humberto da Luz Ferreira</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583996550568</v>
+        <v>5583987036171</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Savio</t>
+          <t>Rosilma</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Savio Vinicius Dantas Barreto</t>
+          <t>Rosilma Dias dos Santos</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583999809811</v>
+        <v>5531992069031</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carmen Lucia Pereira da Silva</t>
+          <t>Bernardo Augusto Diniz</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583993895589</v>
+        <v>5583999779815</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Debora</t>
+          <t>Marilene</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Debora de Lima</t>
+          <t>Marilene Lins Dias</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583988463537</v>
+        <v>5583991746006</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Uelisson</t>
+          <t>Liriane</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uelisson Silva de Araujo</t>
+          <t>Liriane Machado Bezerra</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988116618</v>
+        <v>5583982108404</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Jaqueline</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Joao Batista Mendes de Albuquerque</t>
+          <t>Jaqueline Bispo dos Santos</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583996808715</v>
+        <v>5583987602629</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Mayara</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sandoval Vieira de Melo Junior</t>
+          <t>Mayara Teixeira de Sousa</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583993372828</v>
+        <v>5583988656618</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>José Flávio Aleixo de Sena</t>
+          <t>Felipe Rodrigues dos Santos</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583999528959</v>
+        <v>5583999428747</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ednaldo</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ednaldo dos Santos Pereira</t>
+          <t>Carolina Maia</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583996826425</v>
+        <v>5583988507143</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Francisco Pereira da Silva Filho</t>
+          <t>Elaine Pereira de Souza</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583986910567</v>
+        <v>5583987147769</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Neto</t>
+          <t>Reginaldo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Neto Santos</t>
+          <t>Reginaldo Frutuoso de Sousa</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583988194781</v>
+        <v>5583986239122</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eleonoura</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eleonoura da Silva</t>
+          <t>Franklin Figueiredo de Almeida</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583988346776</v>
+        <v>5583988638711</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Solange</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Antonio da Silva</t>
+          <t>Solange Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583991440343</v>
+        <v>5583988146936</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Snap</t>
+          <t>Zuleide</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Snap - Solucoes Integradas</t>
+          <t>Zuleide da Silva</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583999854551</v>
+        <v>5583998373500</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alyson</t>
+          <t>Jonathas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alyson Lopes de Almeida</t>
+          <t>Jonathas Paulo dos Santos Catao</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583988740034</v>
+        <v>5593999014750</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Lucelio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Antonio Jose Barbosa</t>
+          <t>Lucelio de Araujo Morais</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988947422</v>
+        <v>5583986690357</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rerisson</t>
+          <t>Jocimo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rerisson Pereira Sobral</t>
+          <t>Jocimo Freire dos Santos</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583987243649</v>
+        <v>5583987084613</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Gledson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jose Simplicio da Silva</t>
+          <t>Gledson Soares da Soledade</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5554999560047</v>
+        <v>5583993940979</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>G.p.a</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>G.P.A Gerenciamento</t>
+          <t>Antonio Fernandes Lemos</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583987153391</v>
+        <v>5583996550568</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Savio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rodrigo Diniz</t>
+          <t>Savio Vinicius Dantas Barreto</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583991576868</v>
+        <v>5583999809811</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Drogaria</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Drogaria Equilibrio</t>
+          <t>Carmen Lucia Pereira da Silva</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583999567557</v>
+        <v>5583993895589</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kaio</t>
+          <t>Debora</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kaio Pacifico Soares Formiga</t>
+          <t>Debora de Lima</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583988341845</v>
+        <v>5583988463537</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Uelisson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ana Maria Alves da Silva Barbosa</t>
+          <t>Uelisson Silva de Araujo</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583993131962</v>
+        <v>5583988116618</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ricardo</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ricardo Lourenço</t>
+          <t>Joao Batista Mendes de Albuquerque</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5598984820048</v>
+        <v>5583996808715</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Talony</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Talony Poljean Alves de Araujo</t>
+          <t>Sandoval Vieira de Melo Junior</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583987990918</v>
+        <v>5583993372828</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marinsberg</t>
+          <t>José</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marinsberg Ramos de Oliveira</t>
+          <t>José Flávio Aleixo de Sena</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583988354449</v>
+        <v>5583999528959</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rigoberto</t>
+          <t>Ednaldo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rigoberto Araujo Pereira</t>
+          <t>Ednaldo dos Santos Pereira</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583986397104</v>
+        <v>5583996826425</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Maria de Lourdes Silva Amorim</t>
+          <t>Francisco Pereira da Silva Filho</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583986016509</v>
+        <v>5583986910567</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Neto</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charles Philip Orfeo Nobrega Osias</t>
+          <t>Neto Santos</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988379222</v>
+        <v>5583988194781</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vania</t>
+          <t>Eleonoura</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vania de Lima Araujo</t>
+          <t>Eleonoura da Silva</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5571996450615</v>
+        <v>5583988346776</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jean Carlo Miranda Monteiro</t>
+          <t>Antonio da Silva</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583998164584</v>
+        <v>5583991440343</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Snap</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eduardo da Silva</t>
+          <t>Snap - Solucoes Integradas</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583996255574</v>
+        <v>5583999854551</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rommel</t>
+          <t>Alyson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rommel Lucena</t>
+          <t>Alyson Lopes de Almeida</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583986498556</v>
+        <v>5583988740034</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1188,37 +1188,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Antonio Goncalves da Silva</t>
+          <t>Antonio Jose Barbosa</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583987159983</v>
+        <v>5583988947422</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Elis</t>
+          <t>Rerisson</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Elis Regina de Souza</t>
+          <t>Rerisson Pereira Sobral</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583986471786</v>
+        <v>5583987243649</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kaline</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kaline Felipe Martins</t>
+          <t>Jose Simplicio da Silva</t>
         </is>
       </c>
     </row>
